--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/contdid_cosine_weighted_continuous.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/contdid_cosine_weighted_continuous.xlsx
@@ -407,7 +407,7 @@
     <col min="5" max="5" width="8.96125" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="7.7825" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="8.96125" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="7.7825" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="8.96125" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="5.425" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
@@ -515,13 +515,13 @@
         <v>0.0463</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0396</v>
+        <v>0.0336</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.5148</v>
+        <v>-0.0487</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.6075</v>
+        <v>0.1414</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -543,13 +543,13 @@
         <v>-0.0091</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.0097</v>
+        <v>0.0301</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-0.1467</v>
+        <v>-0.0943</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.1285</v>
+        <v>0.076</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -571,13 +571,13 @@
         <v>-0.0214</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0285</v>
+        <v>0.0342</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-0.4258</v>
+        <v>-0.1182</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.383</v>
+        <v>0.0754</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -599,13 +599,13 @@
         <v>0.0058</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0155</v>
+        <v>0.0482</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-0.2144</v>
+        <v>-0.1306</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.226</v>
+        <v>0.1423</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -627,13 +627,13 @@
         <v>0.0306</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0516</v>
+        <v>0.0448</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-0.7008</v>
+        <v>-0.0962</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.7619</v>
+        <v>0.1574</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -655,13 +655,13 @@
         <v>0.1561</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0656</v>
+        <v>0.0818</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-0.7733</v>
+        <v>-0.0755</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.0855</v>
+        <v>0.3877</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -683,16 +683,16 @@
         <v>0.1648</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.0534</v>
+        <v>0.0537</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.5921</v>
+        <v>0.0129</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.9218</v>
+        <v>0.3168</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>11</v>
@@ -711,13 +711,13 @@
         <v>-0.0622</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.0306</v>
+        <v>0.0554</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-0.496</v>
+        <v>-0.2192</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.3717</v>
+        <v>0.0949</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -739,13 +739,13 @@
         <v>0.0927</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.113</v>
+        <v>0.084</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-1.509</v>
+        <v>-0.1453</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.6943</v>
+        <v>0.3306</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -767,13 +767,13 @@
         <v>0.0494</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.0205</v>
+        <v>0.0421</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.2414</v>
+        <v>-0.0698</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.3402</v>
+        <v>0.1685</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -795,16 +795,16 @@
         <v>-0.298</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.1581</v>
+        <v>0.0829</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-2.5374</v>
+        <v>-0.5329</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.9415</v>
+        <v>-0.0631</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>11</v>
@@ -823,16 +823,16 @@
         <v>0.1449</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0394</v>
+        <v>0.0489</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-0.4141</v>
+        <v>0.0063</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.7038</v>
+        <v>0.2835</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>11</v>
@@ -851,16 +851,16 @@
         <v>-0.1054</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0046</v>
+        <v>0.0395</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-0.1707</v>
+        <v>-0.2173</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.04</v>
+        <v>0.0066</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>11</v>
@@ -879,16 +879,16 @@
         <v>-0.1373</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.0606</v>
+        <v>0.0388</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-0.9953</v>
+        <v>-0.2472</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.7206</v>
+        <v>-0.0275</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>11</v>
@@ -907,13 +907,13 @@
         <v>-0.0683</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.0291</v>
+        <v>0.062</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-0.4807</v>
+        <v>-0.2438</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.3442</v>
+        <v>0.1072</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -935,13 +935,13 @@
         <v>0.0221</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.0217</v>
+        <v>0.0921</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-0.2851</v>
+        <v>-0.2388</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.3294</v>
+        <v>0.2831</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -963,13 +963,13 @@
         <v>-0.025</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.0182</v>
+        <v>0.0698</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-0.2836</v>
+        <v>-0.2227</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.2335</v>
+        <v>0.1726</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -991,16 +991,16 @@
         <v>0.2376</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.0546</v>
+        <v>0.0632</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-0.5361</v>
+        <v>0.0586</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.0113</v>
+        <v>0.4167</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>11</v>
@@ -1019,13 +1019,13 @@
         <v>0.0637</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.0346</v>
+        <v>0.044</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-0.4266</v>
+        <v>-0.0608</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.5539</v>
+        <v>0.1882</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1047,13 +1047,13 @@
         <v>-0.104</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.112</v>
+        <v>0.0819</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-1.6908</v>
+        <v>-0.336</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.4828</v>
+        <v>0.1281</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1075,13 +1075,13 @@
         <v>0.1688</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.0984</v>
+        <v>0.111</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-1.2259</v>
+        <v>-0.1456</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.5634</v>
+        <v>0.4831</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1103,13 +1103,13 @@
         <v>0.1495</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.0393</v>
+        <v>0.1499</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-0.4078</v>
+        <v>-0.2751</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.7068</v>
+        <v>0.5741</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1131,13 +1131,13 @@
         <v>0.0264</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.0789</v>
+        <v>0.132</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-1.0913</v>
+        <v>-0.3475</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.1441</v>
+        <v>0.4003</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1159,13 +1159,13 @@
         <v>0.0176</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.2442</v>
+        <v>0.1355</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>-3.4424</v>
+        <v>-0.3663</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>3.4775</v>
+        <v>0.4015</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1187,13 +1187,13 @@
         <v>0.1014</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.1262</v>
+        <v>0.1431</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>-1.6861</v>
+        <v>-0.304</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.8888</v>
+        <v>0.5067</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1215,13 +1215,13 @@
         <v>0.1311</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.0973</v>
+        <v>0.2254</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>-1.2481</v>
+        <v>-0.5073</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1.5102</v>
+        <v>0.7695</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1243,13 +1243,13 @@
         <v>0.0889</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.2648</v>
+        <v>0.1737</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>-3.6624</v>
+        <v>-0.403</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>3.8402</v>
+        <v>0.5809</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1271,13 +1271,13 @@
         <v>0.1522</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.0865</v>
+        <v>0.1872</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-1.0731</v>
+        <v>-0.3781</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1.3775</v>
+        <v>0.6825</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1299,13 +1299,13 @@
         <v>0.2726</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.1982</v>
+        <v>0.1635</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>-2.5361</v>
+        <v>-0.1906</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>3.0813</v>
+        <v>0.7358</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1327,16 +1327,16 @@
         <v>0.398</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.1255</v>
+        <v>0.0891</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-1.3799</v>
+        <v>0.1455</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>2.1759</v>
+        <v>0.6505</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>13</v>
@@ -1355,13 +1355,13 @@
         <v>0.379</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.0074</v>
+        <v>0.0999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.2746</v>
+        <v>0.096</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.4833</v>
+        <v>0.6619</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>12</v>
@@ -1383,13 +1383,13 @@
         <v>0.4798</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.187</v>
+        <v>0.1716</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>-2.1701</v>
+        <v>-0.0061</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>3.1298</v>
+        <v>0.9657</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1411,16 +1411,16 @@
         <v>0.6789</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.1233</v>
+        <v>0.2168</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>-1.0685</v>
+        <v>0.0647</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>2.4262</v>
+        <v>1.2931</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>13</v>
@@ -1439,16 +1439,16 @@
         <v>0.7194</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.1835</v>
+        <v>0.2012</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>-1.88</v>
+        <v>0.1497</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>3.3189</v>
+        <v>1.2892</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>13</v>
@@ -1467,13 +1467,13 @@
         <v>0.5024</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.1633</v>
+        <v>0.1938</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>-1.8107</v>
+        <v>-0.0466</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>2.8155</v>
+        <v>1.0514</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1495,16 +1495,16 @@
         <v>0.652</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.1428</v>
+        <v>0.2024</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>-1.3706</v>
+        <v>0.0786</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>2.6747</v>
+        <v>1.2255</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>13</v>
@@ -1523,16 +1523,16 @@
         <v>0.7301</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.0655</v>
+        <v>0.2315</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>-0.1985</v>
+        <v>0.0743</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1.6587</v>
+        <v>1.3859</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>13</v>
@@ -1551,16 +1551,16 @@
         <v>0.7478</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.1382</v>
+        <v>0.1962</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>-1.2107</v>
+        <v>0.1922</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>2.7064</v>
+        <v>1.3035</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>13</v>
@@ -1579,16 +1579,16 @@
         <v>0.4939</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.0136</v>
+        <v>0.2432</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.301</v>
+        <v>-0.195</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.6867</v>
+        <v>1.1827</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>13</v>
@@ -1607,16 +1607,16 @@
         <v>0.6311</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.1277</v>
+        <v>0.2036</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>-1.178</v>
+        <v>0.0543</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>2.4402</v>
+        <v>1.2079</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>13</v>
@@ -1635,16 +1635,16 @@
         <v>0.7013</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.2605</v>
+        <v>0.1626</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>-2.9898</v>
+        <v>0.2408</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>4.3924</v>
+        <v>1.1618</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>13</v>
@@ -1663,16 +1663,16 @@
         <v>0.7993</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.0658</v>
+        <v>0.1784</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>-0.1337</v>
+        <v>0.294</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1.7323</v>
+        <v>1.3045</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>13</v>
@@ -1691,16 +1691,16 @@
         <v>0.937</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.2504</v>
+        <v>0.1373</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>-2.6113</v>
+        <v>0.5481</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>4.4853</v>
+        <v>1.3258</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>13</v>
@@ -1719,16 +1719,16 @@
         <v>0.896</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.0715</v>
+        <v>0.1514</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>-0.1165</v>
+        <v>0.4671</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1.9085</v>
+        <v>1.325</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>13</v>
@@ -1747,13 +1747,13 @@
         <v>1.1411</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.0156</v>
+        <v>0.2698</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>0.9197</v>
+        <v>0.3769</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1.3624</v>
+        <v>1.9053</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>12</v>
@@ -1775,16 +1775,16 @@
         <v>1.1167</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.1107</v>
+        <v>0.2972</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>-0.4515</v>
+        <v>0.2747</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>2.6849</v>
+        <v>1.9586</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>13</v>
@@ -1803,16 +1803,16 @@
         <v>1.1373</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.1095</v>
+        <v>0.2144</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.4139</v>
+        <v>0.5301</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>2.6885</v>
+        <v>1.7445</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>13</v>
@@ -1831,16 +1831,16 @@
         <v>1.2158</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.1764</v>
+        <v>0.2601</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-1.2832</v>
+        <v>0.4791</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>3.7149</v>
+        <v>1.9526</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>13</v>
@@ -1859,16 +1859,16 @@
         <v>1.3131</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.265</v>
+        <v>0.322</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-2.4417</v>
+        <v>0.4009</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>5.0679</v>
+        <v>2.2253</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>13</v>
@@ -1887,13 +1887,13 @@
         <v>1.3311</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.0729</v>
+        <v>0.2597</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.2979</v>
+        <v>0.5955</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>2.3642</v>
+        <v>2.0666</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>12</v>
@@ -1915,16 +1915,16 @@
         <v>1.1781</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.1388</v>
+        <v>0.233</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.7889</v>
+        <v>0.5181</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>3.1452</v>
+        <v>1.8381</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>13</v>
@@ -1943,16 +1943,16 @@
         <v>1.2154</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.2283</v>
+        <v>0.2745</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>-2.0193</v>
+        <v>0.4379</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>4.4502</v>
+        <v>1.993</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>13</v>
@@ -1971,16 +1971,16 @@
         <v>1.3023</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.1087</v>
+        <v>0.2629</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>-0.2379</v>
+        <v>0.5575</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>2.8425</v>
+        <v>2.0471</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>13</v>
@@ -1999,13 +1999,13 @@
         <v>1.4084</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.0647</v>
+        <v>0.1939</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>0.492</v>
+        <v>0.8593</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>2.3247</v>
+        <v>1.9575</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>12</v>
@@ -2027,16 +2027,16 @@
         <v>1.4357</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.1033</v>
+        <v>0.1415</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>-0.028</v>
+        <v>1.0351</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>2.8995</v>
+        <v>1.8364</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>13</v>
@@ -2055,16 +2055,16 @@
         <v>1.5096</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.1282</v>
+        <v>0.2039</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>-0.3061</v>
+        <v>0.9319</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>3.3253</v>
+        <v>2.0873</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>13</v>
@@ -2083,16 +2083,16 @@
         <v>1.7718</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.1407</v>
+        <v>0.293</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>-0.2213</v>
+        <v>0.9418</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>3.7649</v>
+        <v>2.6017</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>13</v>
@@ -2111,13 +2111,13 @@
         <v>1.7318</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.0852</v>
+        <v>0.3157</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>0.5251</v>
+        <v>0.8377</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>2.9385</v>
+        <v>2.6259</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>12</v>
@@ -2139,16 +2139,16 @@
         <v>1.4025</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.3288</v>
+        <v>0.2851</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>-3.2566</v>
+        <v>0.595</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>6.0616</v>
+        <v>2.2101</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>13</v>
@@ -2167,16 +2167,16 @@
         <v>1.5421</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.1365</v>
+        <v>0.2431</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>-0.3925</v>
+        <v>0.8534</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>3.4767</v>
+        <v>2.2308</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>13</v>
@@ -2195,16 +2195,16 @@
         <v>1.6159</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.3753</v>
+        <v>0.3569</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>-3.7021</v>
+        <v>0.6051</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>6.9338</v>
+        <v>2.6266</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>13</v>
@@ -2223,16 +2223,16 @@
         <v>1.5598</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.1102</v>
+        <v>0.2449</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>-0.0012</v>
+        <v>0.8661</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>3.1209</v>
+        <v>2.2535</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>13</v>
